--- a/docs/PlayEdu后台API-Controller测试跟踪.xlsx
+++ b/docs/PlayEdu后台API-Controller测试跟踪.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="R0aae178ec7714393"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controller明细" sheetId="2" r:id="R44125445c2c64e03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="R5d7b7020c2c94a17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controller明细" sheetId="2" r:id="Rddc19e81416640ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -352,7 +352,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -363,7 +363,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -374,7 +374,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -385,7 +385,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -396,7 +396,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -407,7 +407,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -418,7 +418,7 @@
         <x:color rgb="FF1D4ED8"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDBEAFE"/>
         </x:patternFill>
       </x:fill>
@@ -429,7 +429,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -440,7 +440,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -783,13 +783,13 @@
         <x:v>完整业务测试</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>题库、试卷</x:v>
+        <x:v>登录、题库、试卷</x:v>
       </x:c>
       <x:c r="E6" s="15" t="str">
         <x:v>待补业务测试</x:v>
       </x:c>
       <x:c r="F6" s="16" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G6" s="1"/>
       <x:c r="H6" s="1"/>
@@ -857,7 +857,7 @@
       </x:c>
       <x:c r="E9" s="51" t="str">
         <x:f>IF(COUNTIFS('Controller明细'!$A$6:$A$28,A9,'Controller明细'!$F$6:$F$28,"&lt;&gt;已覆盖")=0,"已覆盖","待补充")</x:f>
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F9" s="51" t="str">
         <x:v>P0</x:v>
@@ -1197,7 +1197,7 @@
       </x:c>
       <x:c r="E20" s="59" t="str">
         <x:f>COUNTIF(E9:E19,"已覆盖")&amp;"/"&amp;COUNTA(E9:E19)&amp;" 类已覆盖"</x:f>
-        <x:v>2/11 类已覆盖</x:v>
+        <x:v>3/11 类已覆盖</x:v>
       </x:c>
       <x:c r="F20" s="59"/>
       <x:c r="G20" s="59"/>
@@ -1477,7 +1477,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cb37063c3164108"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec5e238c1c8647c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1607,7 +1607,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F6" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G6" s="51" t="str">
         <x:v>P0</x:v>
@@ -1615,7 +1615,7 @@
       <x:c r="H6" s="61" t="str"/>
       <x:c r="I6" s="65"/>
       <x:c r="J6" s="49" t="str">
-        <x:v>登录、退出、详情、修改密码</x:v>
+        <x:v>15个HTTP用例，覆盖4个接口及认证异常分支</x:v>
       </x:c>
       <x:c r="K6" s="1"/>
     </x:row>
@@ -2438,7 +2438,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e41f8f7a0264ca1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R673ec174627d4e03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/PlayEdu后台API-Controller测试跟踪.xlsx
+++ b/docs/PlayEdu后台API-Controller测试跟踪.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="R5d7b7020c2c94a17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controller明细" sheetId="2" r:id="Rddc19e81416640ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="Rb571540f189743fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controller明细" sheetId="2" r:id="Rae44be0f7a9a4362"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -783,13 +783,13 @@
         <x:v>完整业务测试</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>登录、题库、试卷</x:v>
+        <x:v>登录、管理员权限、题库、试卷</x:v>
       </x:c>
       <x:c r="E6" s="15" t="str">
         <x:v>待补业务测试</x:v>
       </x:c>
       <x:c r="F6" s="16" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G6" s="1"/>
       <x:c r="H6" s="1"/>
@@ -888,7 +888,7 @@
       </x:c>
       <x:c r="E10" s="51" t="str">
         <x:f>IF(COUNTIFS('Controller明细'!$A$6:$A$28,A10,'Controller明细'!$F$6:$F$28,"&lt;&gt;已覆盖")=0,"已覆盖","待补充")</x:f>
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F10" s="51" t="str">
         <x:v>P0</x:v>
@@ -1197,7 +1197,7 @@
       </x:c>
       <x:c r="E20" s="59" t="str">
         <x:f>COUNTIF(E9:E19,"已覆盖")&amp;"/"&amp;COUNTA(E9:E19)&amp;" 类已覆盖"</x:f>
-        <x:v>3/11 类已覆盖</x:v>
+        <x:v>4/11 类已覆盖</x:v>
       </x:c>
       <x:c r="F20" s="59"/>
       <x:c r="G20" s="59"/>
@@ -1477,7 +1477,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec5e238c1c8647c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raca6dc02944d4393"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1636,7 +1636,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F7" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G7" s="51" t="str">
         <x:v>P0</x:v>
@@ -1644,7 +1644,7 @@
       <x:c r="H7" s="61" t="str"/>
       <x:c r="I7" s="65"/>
       <x:c r="J7" s="49" t="str">
-        <x:v>管理员账号管理</x:v>
+        <x:v>14个HTTP用例覆盖鉴权、校验、筛选、角色分配与增删改</x:v>
       </x:c>
       <x:c r="K7" s="1"/>
     </x:row>
@@ -1665,7 +1665,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F8" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G8" s="51" t="str">
         <x:v>P0</x:v>
@@ -1673,7 +1673,7 @@
       <x:c r="H8" s="61" t="str"/>
       <x:c r="I8" s="65"/>
       <x:c r="J8" s="49" t="str">
-        <x:v>角色与权限管理</x:v>
+        <x:v>覆盖权限分组、角色增删改及超级管理员角色保护</x:v>
       </x:c>
       <x:c r="K8" s="1"/>
     </x:row>
@@ -2438,7 +2438,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R673ec174627d4e03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24eb4d8124a64f64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/PlayEdu后台API-Controller测试跟踪.xlsx
+++ b/docs/PlayEdu后台API-Controller测试跟踪.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="Rb571540f189743fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controller明细" sheetId="2" r:id="Rae44be0f7a9a4362"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="Rb7606df4c88f4788"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controller明细" sheetId="2" r:id="Rb55f40a6ed774fb7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -783,13 +783,13 @@
         <x:v>完整业务测试</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>登录、管理员权限、题库、试卷</x:v>
+        <x:v>登录、管理员权限、用户、部门、课程、资源与上传、题库、试卷、系统配置与运维、数据看板</x:v>
       </x:c>
       <x:c r="E6" s="15" t="str">
         <x:v>待补业务测试</x:v>
       </x:c>
       <x:c r="F6" s="16" t="n">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G6" s="1"/>
       <x:c r="H6" s="1"/>
@@ -919,7 +919,7 @@
       </x:c>
       <x:c r="E11" s="51" t="str">
         <x:f>IF(COUNTIFS('Controller明细'!$A$6:$A$28,A11,'Controller明细'!$F$6:$F$28,"&lt;&gt;已覆盖")=0,"已覆盖","待补充")</x:f>
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F11" s="51" t="str">
         <x:v>P0</x:v>
@@ -950,7 +950,7 @@
       </x:c>
       <x:c r="E12" s="51" t="str">
         <x:f>IF(COUNTIFS('Controller明细'!$A$6:$A$28,A12,'Controller明细'!$F$6:$F$28,"&lt;&gt;已覆盖")=0,"已覆盖","待补充")</x:f>
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F12" s="51" t="str">
         <x:v>P0</x:v>
@@ -1012,7 +1012,7 @@
       </x:c>
       <x:c r="E14" s="51" t="str">
         <x:f>IF(COUNTIFS('Controller明细'!$A$6:$A$28,A14,'Controller明细'!$F$6:$F$28,"&lt;&gt;已覆盖")=0,"已覆盖","待补充")</x:f>
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F14" s="51" t="str">
         <x:v>P0</x:v>
@@ -1043,7 +1043,7 @@
       </x:c>
       <x:c r="E15" s="51" t="str">
         <x:f>IF(COUNTIFS('Controller明细'!$A$6:$A$28,A15,'Controller明细'!$F$6:$F$28,"&lt;&gt;已覆盖")=0,"已覆盖","待补充")</x:f>
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F15" s="51" t="str">
         <x:v>P1</x:v>
@@ -1136,7 +1136,7 @@
       </x:c>
       <x:c r="E18" s="51" t="str">
         <x:f>IF(COUNTIFS('Controller明细'!$A$6:$A$28,A18,'Controller明细'!$F$6:$F$28,"&lt;&gt;已覆盖")=0,"已覆盖","待补充")</x:f>
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F18" s="51" t="str">
         <x:v>P2</x:v>
@@ -1167,7 +1167,7 @@
       </x:c>
       <x:c r="E19" s="55" t="str">
         <x:f>IF(COUNTIFS('Controller明细'!$A$6:$A$28,A19,'Controller明细'!$F$6:$F$28,"&lt;&gt;已覆盖")=0,"已覆盖","待补充")</x:f>
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F19" s="55" t="str">
         <x:v>P2</x:v>
@@ -1197,7 +1197,7 @@
       </x:c>
       <x:c r="E20" s="59" t="str">
         <x:f>COUNTIF(E9:E19,"已覆盖")&amp;"/"&amp;COUNTA(E9:E19)&amp;" 类已覆盖"</x:f>
-        <x:v>4/11 类已覆盖</x:v>
+        <x:v>10/11 类已覆盖</x:v>
       </x:c>
       <x:c r="F20" s="59"/>
       <x:c r="G20" s="59"/>
@@ -1477,7 +1477,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raca6dc02944d4393"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6552e7c92354a79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1694,7 +1694,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F9" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G9" s="51" t="str">
         <x:v>P0</x:v>
@@ -1702,7 +1702,7 @@
       <x:c r="H9" s="61" t="str"/>
       <x:c r="I9" s="65"/>
       <x:c r="J9" s="49" t="str">
-        <x:v>学员及学习数据管理</x:v>
+        <x:v>覆盖用户校验、批量导入、学习记录及增删改</x:v>
       </x:c>
       <x:c r="K9" s="1"/>
     </x:row>
@@ -1723,7 +1723,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F10" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G10" s="51" t="str">
         <x:v>P0</x:v>
@@ -1731,7 +1731,7 @@
       <x:c r="H10" s="61" t="str"/>
       <x:c r="I10" s="65"/>
       <x:c r="J10" s="49" t="str">
-        <x:v>部门、成员和组织层级</x:v>
+        <x:v>覆盖层级统计、关联预检、排序迁移、LDAP限制与同步</x:v>
       </x:c>
       <x:c r="K10" s="1"/>
     </x:row>
@@ -1810,7 +1810,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F13" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G13" s="51" t="str">
         <x:v>P0</x:v>
@@ -1818,7 +1818,7 @@
       <x:c r="H13" s="61" t="str"/>
       <x:c r="I13" s="65"/>
       <x:c r="J13" s="49" t="str">
-        <x:v>课程管理</x:v>
+        <x:v>覆盖筛选、创建配置、归属权限及增删改</x:v>
       </x:c>
       <x:c r="K13" s="1"/>
     </x:row>
@@ -1839,7 +1839,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F14" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G14" s="51" t="str">
         <x:v>P0</x:v>
@@ -1847,7 +1847,7 @@
       <x:c r="H14" s="61" t="str"/>
       <x:c r="I14" s="65"/>
       <x:c r="J14" s="49" t="str">
-        <x:v>课程章节</x:v>
+        <x:v>覆盖增删改、排序及存在课时禁止删除</x:v>
       </x:c>
       <x:c r="K14" s="1"/>
     </x:row>
@@ -1868,7 +1868,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F15" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G15" s="51" t="str">
         <x:v>P0</x:v>
@@ -1876,7 +1876,7 @@
       <x:c r="H15" s="61" t="str"/>
       <x:c r="I15" s="65"/>
       <x:c r="J15" s="49" t="str">
-        <x:v>课程课时</x:v>
+        <x:v>覆盖类型、重复资源、批量导入及增删改排序</x:v>
       </x:c>
       <x:c r="K15" s="1"/>
     </x:row>
@@ -1897,7 +1897,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F16" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G16" s="51" t="str">
         <x:v>P0</x:v>
@@ -1905,7 +1905,7 @@
       <x:c r="H16" s="61" t="str"/>
       <x:c r="I16" s="65"/>
       <x:c r="J16" s="49" t="str">
-        <x:v>课程附件</x:v>
+        <x:v>覆盖类型、重复附件、批量导入及增删改排序</x:v>
       </x:c>
       <x:c r="K16" s="1"/>
     </x:row>
@@ -1926,7 +1926,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F17" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G17" s="51" t="str">
         <x:v>P0</x:v>
@@ -1934,7 +1934,7 @@
       <x:c r="H17" s="61" t="str"/>
       <x:c r="I17" s="65"/>
       <x:c r="J17" s="49" t="str">
-        <x:v>附件下载记录</x:v>
+        <x:v>覆盖分页及学员、课程、附件筛选</x:v>
       </x:c>
       <x:c r="K17" s="1"/>
     </x:row>
@@ -1955,7 +1955,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F18" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G18" s="51" t="str">
         <x:v>P0</x:v>
@@ -1963,7 +1963,7 @@
       <x:c r="H18" s="61" t="str"/>
       <x:c r="I18" s="65"/>
       <x:c r="J18" s="49" t="str">
-        <x:v>课程学员关联</x:v>
+        <x:v>覆盖学员筛选、学习记录及批量删除</x:v>
       </x:c>
       <x:c r="K18" s="1"/>
     </x:row>
@@ -1984,7 +1984,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F19" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G19" s="51" t="str">
         <x:v>P1</x:v>
@@ -1992,7 +1992,7 @@
       <x:c r="H19" s="61" t="str"/>
       <x:c r="I19" s="65"/>
       <x:c r="J19" s="49" t="str">
-        <x:v>资源文件管理</x:v>
+        <x:v>覆盖类型校验、分类筛选、归属权限及增删改</x:v>
       </x:c>
       <x:c r="K19" s="1"/>
     </x:row>
@@ -2013,7 +2013,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F20" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G20" s="51" t="str">
         <x:v>P1</x:v>
@@ -2021,7 +2021,7 @@
       <x:c r="H20" s="61" t="str"/>
       <x:c r="I20" s="65"/>
       <x:c r="J20" s="49" t="str">
-        <x:v>资源分类</x:v>
+        <x:v>覆盖分类查询、关联预检、增删改、排序和迁移</x:v>
       </x:c>
       <x:c r="K20" s="1"/>
     </x:row>
@@ -2042,7 +2042,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F21" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G21" s="51" t="str">
         <x:v>P1</x:v>
@@ -2050,7 +2050,7 @@
       <x:c r="H21" s="61" t="str"/>
       <x:c r="I21" s="65"/>
       <x:c r="J21" s="49" t="str">
-        <x:v>普通上传和分片上传</x:v>
+        <x:v>覆盖存储配置、格式校验、普通上传及分片接口契约</x:v>
       </x:c>
       <x:c r="K21" s="1"/>
     </x:row>
@@ -2129,7 +2129,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F24" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G24" s="51" t="str">
         <x:v>P2</x:v>
@@ -2137,7 +2137,7 @@
       <x:c r="H24" s="61" t="str"/>
       <x:c r="I24" s="65"/>
       <x:c r="J24" s="49" t="str">
-        <x:v>应用配置</x:v>
+        <x:v>覆盖私密配置脱敏、图片地址和存储端点归一化</x:v>
       </x:c>
       <x:c r="K24" s="1"/>
     </x:row>
@@ -2158,7 +2158,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F25" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G25" s="51" t="str">
         <x:v>P2</x:v>
@@ -2166,7 +2166,7 @@
       <x:c r="H25" s="61" t="str"/>
       <x:c r="I25" s="65"/>
       <x:c r="J25" s="49" t="str">
-        <x:v>系统基础数据</x:v>
+        <x:v>覆盖品牌配置、默认头像、部门与资源分类数据</x:v>
       </x:c>
       <x:c r="K25" s="1"/>
     </x:row>
@@ -2187,7 +2187,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F26" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G26" s="51" t="str">
         <x:v>P2</x:v>
@@ -2195,7 +2195,7 @@
       <x:c r="H26" s="61" t="str"/>
       <x:c r="I26" s="65"/>
       <x:c r="J26" s="49" t="str">
-        <x:v>缓存管理</x:v>
+        <x:v>覆盖缓存列表、单键删除和全部清理</x:v>
       </x:c>
       <x:c r="K26" s="1"/>
     </x:row>
@@ -2216,7 +2216,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F27" s="51" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G27" s="51" t="str">
         <x:v>P2</x:v>
@@ -2224,7 +2224,7 @@
       <x:c r="H27" s="61" t="str"/>
       <x:c r="I27" s="65"/>
       <x:c r="J27" s="49" t="str">
-        <x:v>后台操作日志</x:v>
+        <x:v>覆盖权限、归属筛选、条件分页及详情异常</x:v>
       </x:c>
       <x:c r="K27" s="1"/>
     </x:row>
@@ -2245,7 +2245,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="F28" s="55" t="str">
-        <x:v>待补充</x:v>
+        <x:v>已覆盖</x:v>
       </x:c>
       <x:c r="G28" s="55" t="str">
         <x:v>P2</x:v>
@@ -2253,7 +2253,7 @@
       <x:c r="H28" s="62" t="str"/>
       <x:c r="I28" s="66"/>
       <x:c r="J28" s="53" t="str">
-        <x:v>后台首页统计</x:v>
+        <x:v>覆盖用户、课程、资源、组织及学习排行统计</x:v>
       </x:c>
       <x:c r="K28" s="1"/>
     </x:row>
@@ -2438,7 +2438,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24eb4d8124a64f64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d85d9201fd1451d"/>
   </x:tableParts>
 </x:worksheet>
 </file>